--- a/data/02_運用_rakuten.xlsx
+++ b/data/02_運用_rakuten.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ca29965d2a6599a/01_資産管理/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="653" documentId="13_ncr:1_{F23918F6-93A0-4FFC-9C54-3B208A91E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC333871-D026-4D34-B7C9-C8F3DDF947DF}"/>
+  <xr:revisionPtr revIDLastSave="667" documentId="13_ncr:1_{F23918F6-93A0-4FFC-9C54-3B208A91E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B8B5871-07A0-49EA-B826-0AB6072A9C4B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7522" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7673" uniqueCount="480">
   <si>
     <t>約定日</t>
   </si>
@@ -2128,6 +2128,9 @@
   <si>
     <t>任天堂</t>
   </si>
+  <si>
+    <t>京都フィナンシャルＧ</t>
+  </si>
 </sst>
 </file>
 
@@ -3430,7 +3433,7 @@
       </c>
       <c r="V2" s="49">
         <f ca="1">TODAY()</f>
-        <v>46199</v>
+        <v>46207</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.45">
@@ -3487,31 +3490,31 @@
       </c>
       <c r="D4" s="20">
         <f>SUM(D5:D100)</f>
-        <v>514445</v>
+        <v>519145</v>
       </c>
       <c r="E4" s="35">
         <f>SUM(B4:D4)</f>
-        <v>3177105</v>
+        <v>3181805</v>
       </c>
       <c r="F4" s="20">
         <f>SUM(F5:F100)</f>
-        <v>13664792</v>
+        <v>14015292</v>
       </c>
       <c r="G4" s="20">
         <f>SUM(G5:G100)</f>
-        <v>-5372687</v>
+        <v>-5393677</v>
       </c>
       <c r="H4" s="20">
         <f>SUM(H5:H100)</f>
-        <v>870235</v>
+        <v>916435</v>
       </c>
       <c r="I4" s="35">
         <f>SUM(F4:H4)</f>
-        <v>9162340</v>
+        <v>9538050</v>
       </c>
       <c r="J4" s="35">
         <f>SUM(J5:J100)</f>
-        <v>7301010.6289999997</v>
+        <v>7600395.1425000001</v>
       </c>
       <c r="K4" s="20">
         <f>SUM(K5:K100)</f>
@@ -3519,15 +3522,15 @@
       </c>
       <c r="L4" s="20">
         <f>SUM(L5:L100)</f>
-        <v>-678053</v>
+        <v>-1192189</v>
       </c>
       <c r="M4" s="35">
         <f>SUM(K4:L4)</f>
-        <v>-203805</v>
+        <v>-717941</v>
       </c>
       <c r="N4" s="35">
         <f>SUM(N5:N100)</f>
-        <v>-258697.95835</v>
+        <v>-719996.67485000007</v>
       </c>
       <c r="O4" s="20">
         <f>SUM(O5:O100)</f>
@@ -3547,11 +3550,11 @@
       </c>
       <c r="S4" s="38">
         <f>SUM(E4,J4,N4,R4)</f>
-        <v>10370992.883950001</v>
+        <v>10213778.680950001</v>
       </c>
       <c r="U4" s="56">
         <f ca="1">(V2-U2)/365</f>
-        <v>5.6273972602739724</v>
+        <v>5.6493150684931503</v>
       </c>
       <c r="V4" s="56"/>
     </row>
@@ -3576,11 +3579,11 @@
         <v>160060</v>
       </c>
       <c r="F5" s="19">
-        <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2021/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2021/12/31",国内株式_特定!$N$2:$N$998,"&gt;=0")</f>
+        <f>SUMIFS(国内株式_特定!$N$2:$N$996,国内株式_特定!$B$2:$B$996,"&gt;=2021/1/1",国内株式_特定!$B$2:$B$996,"&lt;=2021/12/31",国内株式_特定!$N$2:$N$996,"&gt;=0")</f>
         <v>630746</v>
       </c>
       <c r="G5" s="19">
-        <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2021/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2021/12/31",国内株式_特定!$N$2:$N$998,"&lt;0")</f>
+        <f>SUMIFS(国内株式_特定!$N$2:$N$996,国内株式_特定!$B$2:$B$996,"&gt;=2021/1/1",国内株式_特定!$B$2:$B$996,"&lt;=2021/12/31",国内株式_特定!$N$2:$N$996,"&lt;0")</f>
         <v>-601144</v>
       </c>
       <c r="H5" s="19">
@@ -3653,11 +3656,11 @@
         <v>35720</v>
       </c>
       <c r="F6" s="19">
-        <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2022/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2022/12/31",国内株式_特定!$N$2:$N$998,"&gt;=0")</f>
+        <f>SUMIFS(国内株式_特定!$N$2:$N$996,国内株式_特定!$B$2:$B$996,"&gt;=2022/1/1",国内株式_特定!$B$2:$B$996,"&lt;=2022/12/31",国内株式_特定!$N$2:$N$996,"&gt;=0")</f>
         <v>619915</v>
       </c>
       <c r="G6" s="19">
-        <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2022/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2022/12/31",国内株式_特定!$N$2:$N$998,"&lt;0")</f>
+        <f>SUMIFS(国内株式_特定!$N$2:$N$996,国内株式_特定!$B$2:$B$996,"&gt;=2022/1/1",国内株式_特定!$B$2:$B$996,"&lt;=2022/12/31",国内株式_特定!$N$2:$N$996,"&lt;0")</f>
         <v>-699020</v>
       </c>
       <c r="H6" s="19">
@@ -3730,11 +3733,11 @@
         <v>214320</v>
       </c>
       <c r="F7" s="19">
-        <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2023/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2023/12/31",国内株式_特定!$N$2:$N$998,"&gt;=0")</f>
+        <f>SUMIFS(国内株式_特定!$N$2:$N$996,国内株式_特定!$B$2:$B$996,"&gt;=2023/1/1",国内株式_特定!$B$2:$B$996,"&lt;=2023/12/31",国内株式_特定!$N$2:$N$996,"&gt;=0")</f>
         <v>1679057</v>
       </c>
       <c r="G7" s="19">
-        <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2023/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2023/12/31",国内株式_特定!$N$2:$N$998,"&lt;0")</f>
+        <f>SUMIFS(国内株式_特定!$N$2:$N$996,国内株式_特定!$B$2:$B$996,"&gt;=2023/1/1",国内株式_特定!$B$2:$B$996,"&lt;=2023/12/31",国内株式_特定!$N$2:$N$996,"&lt;0")</f>
         <v>-402270</v>
       </c>
       <c r="H7" s="19">
@@ -3807,11 +3810,11 @@
         <v>111775</v>
       </c>
       <c r="F8" s="19">
-        <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2024/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2024/12/31",国内株式_特定!$N$2:$N$998,"&gt;=0")</f>
+        <f>SUMIFS(国内株式_特定!$N$2:$N$996,国内株式_特定!$B$2:$B$996,"&gt;=2024/1/1",国内株式_特定!$B$2:$B$996,"&lt;=2024/12/31",国内株式_特定!$N$2:$N$996,"&gt;=0")</f>
         <v>2059210</v>
       </c>
       <c r="G8" s="19">
-        <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2024/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2024/12/31",国内株式_特定!$N$2:$N$998,"&lt;0")</f>
+        <f>SUMIFS(国内株式_特定!$N$2:$N$996,国内株式_特定!$B$2:$B$996,"&gt;=2024/1/1",国内株式_特定!$B$2:$B$996,"&lt;=2024/12/31",国内株式_特定!$N$2:$N$996,"&lt;0")</f>
         <v>-1123620</v>
       </c>
       <c r="H8" s="19">
@@ -3884,11 +3887,11 @@
         <v>2647720</v>
       </c>
       <c r="F9" s="19">
-        <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2025/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2025/12/31",国内株式_特定!$N$2:$N$998,"&gt;=0")</f>
+        <f>SUMIFS(国内株式_特定!$N$2:$N$996,国内株式_特定!$B$2:$B$996,"&gt;=2025/1/1",国内株式_特定!$B$2:$B$996,"&lt;=2025/12/31",国内株式_特定!$N$2:$N$996,"&gt;=0")</f>
         <v>2657465</v>
       </c>
       <c r="G9" s="19">
-        <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2025/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2025/12/31",国内株式_特定!$N$2:$N$998,"&lt;0")</f>
+        <f>SUMIFS(国内株式_特定!$N$2:$N$996,国内株式_特定!$B$2:$B$996,"&gt;=2025/1/1",国内株式_特定!$B$2:$B$996,"&lt;=2025/12/31",国内株式_特定!$N$2:$N$996,"&lt;0")</f>
         <v>-599245</v>
       </c>
       <c r="H9" s="19">
@@ -3954,31 +3957,31 @@
       </c>
       <c r="D10" s="19">
         <f>SUMIFS(国内株式_NISA_配当!$K$2:$K$1004,国内株式_NISA_配当!$A$2:$A$1004,"&gt;=2026/1/1",国内株式_NISA_配当!$A$2:$A$1004,"&lt;=2026/12/31")</f>
-        <v>64150</v>
+        <v>68850</v>
       </c>
       <c r="E10" s="35">
         <f t="shared" si="7"/>
-        <v>7510</v>
+        <v>12210</v>
       </c>
       <c r="F10" s="19">
-        <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$998,"&gt;=0")</f>
-        <v>6018399</v>
+        <f>SUMIFS(国内株式_特定!$N$2:$N$996,国内株式_特定!$B$2:$B$996,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$996,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$996,"&gt;=0")</f>
+        <v>6368899</v>
       </c>
       <c r="G10" s="19">
-        <f>SUMIFS(国内株式_特定!$N$2:$N$998,国内株式_特定!$B$2:$B$998,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$998,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$998,"&lt;0")</f>
-        <v>-1947388</v>
+        <f>SUMIFS(国内株式_特定!$N$2:$N$996,国内株式_特定!$B$2:$B$996,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$996,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$996,"&lt;0")</f>
+        <v>-1968378</v>
       </c>
       <c r="H10" s="19">
         <f>SUMIFS(国内株式_特定_配当!$H$2:$H$999,国内株式_特定_配当!$A$2:$A$999,"&gt;=2026/1/1",国内株式_特定_配当!$A$2:$A$999,"&lt;=2026/12/31")</f>
-        <v>68080</v>
+        <v>114280</v>
       </c>
       <c r="I10" s="35">
         <f t="shared" si="11"/>
-        <v>4139091</v>
+        <v>4514801</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="1"/>
-        <v>3298234.66335</v>
+        <v>3597619.1768499999</v>
       </c>
       <c r="K10" s="19">
         <f>SUMIFS(国内株式_信用!$P$2:$P$1000,国内株式_信用!$B$2:$B$1000,"&gt;=2026/1/1",国内株式_信用!$B$2:$B$1000,"&lt;=2026/12/31",国内株式_信用!$P$2:$P$1000,"&gt;=0")</f>
@@ -3986,15 +3989,15 @@
       </c>
       <c r="L10" s="19">
         <f>SUMIFS(国内株式_信用!$P$2:$P$1000,国内株式_信用!$B$2:$B$1000,"&gt;=2026/1/1",国内株式_信用!$B$2:$B$1000,"&lt;=2026/12/31",国内株式_信用!$P$2:$P$1000,"&lt;0")</f>
-        <v>-3810</v>
+        <v>-517946</v>
       </c>
       <c r="M10" s="35">
         <f t="shared" si="12"/>
-        <v>260090</v>
+        <v>-254046</v>
       </c>
       <c r="N10" s="36">
         <f t="shared" si="13"/>
-        <v>207252.71650000001</v>
+        <v>-254046</v>
       </c>
       <c r="O10" s="19">
         <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2026/1/1",投資信託!$B$2:$B$1033,"&lt;=2026/12/31",投資信託!$K$2:$K$1033,"&gt;=0")</f>
@@ -4014,7 +4017,7 @@
       </c>
       <c r="S10" s="38">
         <f>SUM(E10,J10,N10,R10)</f>
-        <v>3512997.3798500001</v>
+        <v>3355783.1768499999</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.45">
@@ -10112,7 +10115,7 @@
   <sheetPr>
     <tabColor theme="7" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K68"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.19921875" style="1" bestFit="1" customWidth="1"/>
@@ -12540,18 +12543,18 @@
         <v>100</v>
       </c>
       <c r="H64" s="19">
-        <f t="shared" ref="H64:H67" si="6">F64*G64</f>
+        <f t="shared" ref="H64:H68" si="6">F64*G64</f>
         <v>4000</v>
       </c>
       <c r="I64" s="19">
         <v>0</v>
       </c>
       <c r="J64" s="19">
-        <f t="shared" ref="J64:J67" si="7">H64-I64</f>
+        <f t="shared" ref="J64:J68" si="7">H64-I64</f>
         <v>4000</v>
       </c>
       <c r="K64" s="19">
-        <f t="shared" ref="K64:K67" si="8">J64</f>
+        <f t="shared" ref="K64:K68" si="8">J64</f>
         <v>4000</v>
       </c>
     </row>
@@ -12667,6 +12670,44 @@
       <c r="K67" s="19">
         <f t="shared" si="8"/>
         <v>10000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A68" s="4">
+        <v>46203</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="D68" s="5">
+        <v>1802</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F68" s="23">
+        <v>47</v>
+      </c>
+      <c r="G68" s="5">
+        <v>100</v>
+      </c>
+      <c r="H68" s="19">
+        <f t="shared" si="6"/>
+        <v>4700</v>
+      </c>
+      <c r="I68" s="19">
+        <v>0</v>
+      </c>
+      <c r="J68" s="19">
+        <f t="shared" si="7"/>
+        <v>4700</v>
+      </c>
+      <c r="K68" s="19">
+        <f t="shared" si="8"/>
+        <v>4700</v>
       </c>
     </row>
   </sheetData>
@@ -12686,7 +12727,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:O981"/>
+  <dimension ref="A1:O992"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
@@ -54904,7 +54945,7 @@
         <v>31</v>
       </c>
       <c r="M938" s="15">
-        <f t="shared" ref="M938:M981" si="21">IF(G938="買付",H938*I938+SUM(J938:K938),H938*I938-SUM(J938:K938))</f>
+        <f t="shared" ref="M938:M992" si="21">IF(G938="買付",H938*I938+SUM(J938:K938),H938*I938-SUM(J938:K938))</f>
         <v>526900</v>
       </c>
       <c r="N938" s="19">
@@ -56845,6 +56886,501 @@
       </c>
       <c r="N981" s="19">
         <v>0</v>
+      </c>
+    </row>
+    <row r="982" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A982" s="4">
+        <v>46202</v>
+      </c>
+      <c r="B982" s="4">
+        <v>46204</v>
+      </c>
+      <c r="C982" s="5">
+        <v>5844</v>
+      </c>
+      <c r="D982" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="E982" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F982" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G982" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H982" s="5">
+        <v>100</v>
+      </c>
+      <c r="I982" s="7">
+        <v>4496.5</v>
+      </c>
+      <c r="J982" s="9">
+        <v>0</v>
+      </c>
+      <c r="K982" s="9">
+        <v>0</v>
+      </c>
+      <c r="L982" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M982" s="15">
+        <f t="shared" si="21"/>
+        <v>449650</v>
+      </c>
+      <c r="N982" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="983" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A983" s="4">
+        <v>46202</v>
+      </c>
+      <c r="B983" s="4">
+        <v>46204</v>
+      </c>
+      <c r="C983" s="5">
+        <v>6324</v>
+      </c>
+      <c r="D983" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="E983" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F983" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G983" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H983" s="5">
+        <v>100</v>
+      </c>
+      <c r="I983" s="7">
+        <v>7120</v>
+      </c>
+      <c r="J983" s="9">
+        <v>0</v>
+      </c>
+      <c r="K983" s="9">
+        <v>0</v>
+      </c>
+      <c r="L983" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M983" s="15">
+        <f t="shared" si="21"/>
+        <v>712000</v>
+      </c>
+      <c r="N983" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="984" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A984" s="4">
+        <v>46202</v>
+      </c>
+      <c r="B984" s="4">
+        <v>46204</v>
+      </c>
+      <c r="C984" s="5">
+        <v>6857</v>
+      </c>
+      <c r="D984" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="E984" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F984" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G984" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H984" s="5">
+        <v>100</v>
+      </c>
+      <c r="I984" s="7">
+        <v>31960</v>
+      </c>
+      <c r="J984" s="9">
+        <v>0</v>
+      </c>
+      <c r="K984" s="9">
+        <v>0</v>
+      </c>
+      <c r="L984" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M984" s="15">
+        <f t="shared" si="21"/>
+        <v>3196000</v>
+      </c>
+      <c r="N984" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="985" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A985" s="4">
+        <v>46203</v>
+      </c>
+      <c r="B985" s="4">
+        <v>46205</v>
+      </c>
+      <c r="C985" s="5">
+        <v>6857</v>
+      </c>
+      <c r="D985" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="E985" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F985" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G985" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H985" s="5">
+        <v>100</v>
+      </c>
+      <c r="I985" s="7">
+        <v>31750.1</v>
+      </c>
+      <c r="J985" s="9">
+        <v>0</v>
+      </c>
+      <c r="K985" s="9">
+        <v>0</v>
+      </c>
+      <c r="L985" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M985" s="15">
+        <f t="shared" si="21"/>
+        <v>3175010</v>
+      </c>
+      <c r="N985" s="19">
+        <v>-20990</v>
+      </c>
+    </row>
+    <row r="986" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A986" s="4">
+        <v>46203</v>
+      </c>
+      <c r="B986" s="4">
+        <v>46205</v>
+      </c>
+      <c r="C986" s="5">
+        <v>6324</v>
+      </c>
+      <c r="D986" s="9" t="s">
+        <v>454</v>
+      </c>
+      <c r="E986" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F986" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G986" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H986" s="5">
+        <v>100</v>
+      </c>
+      <c r="I986" s="7">
+        <v>7295</v>
+      </c>
+      <c r="J986" s="9">
+        <v>0</v>
+      </c>
+      <c r="K986" s="9">
+        <v>0</v>
+      </c>
+      <c r="L986" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M986" s="15">
+        <f t="shared" si="21"/>
+        <v>729500</v>
+      </c>
+      <c r="N986" s="19">
+        <v>17500</v>
+      </c>
+    </row>
+    <row r="987" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A987" s="4">
+        <v>46203</v>
+      </c>
+      <c r="B987" s="4">
+        <v>46205</v>
+      </c>
+      <c r="C987" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="D987" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="E987" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F987" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G987" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H987" s="5">
+        <v>100</v>
+      </c>
+      <c r="I987" s="7">
+        <v>91050</v>
+      </c>
+      <c r="J987" s="9">
+        <v>0</v>
+      </c>
+      <c r="K987" s="9">
+        <v>0</v>
+      </c>
+      <c r="L987" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M987" s="15">
+        <f t="shared" si="21"/>
+        <v>9105000</v>
+      </c>
+      <c r="N987" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="988" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A988" s="4">
+        <v>46203</v>
+      </c>
+      <c r="B988" s="4">
+        <v>46205</v>
+      </c>
+      <c r="C988" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="D988" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="E988" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F988" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G988" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H988" s="5">
+        <v>100</v>
+      </c>
+      <c r="I988" s="7">
+        <v>91660</v>
+      </c>
+      <c r="J988" s="9">
+        <v>0</v>
+      </c>
+      <c r="K988" s="9">
+        <v>0</v>
+      </c>
+      <c r="L988" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M988" s="15">
+        <f t="shared" si="21"/>
+        <v>9166000</v>
+      </c>
+      <c r="N988" s="19">
+        <v>61000</v>
+      </c>
+    </row>
+    <row r="989" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A989" s="4">
+        <v>46205</v>
+      </c>
+      <c r="B989" s="4">
+        <v>46209</v>
+      </c>
+      <c r="C989" s="5">
+        <v>5844</v>
+      </c>
+      <c r="D989" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="E989" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F989" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G989" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H989" s="5">
+        <v>100</v>
+      </c>
+      <c r="I989" s="7">
+        <v>4653</v>
+      </c>
+      <c r="J989" s="9">
+        <v>0</v>
+      </c>
+      <c r="K989" s="9">
+        <v>0</v>
+      </c>
+      <c r="L989" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M989" s="15">
+        <f t="shared" si="21"/>
+        <v>465300</v>
+      </c>
+      <c r="N989" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="990" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A990" s="4">
+        <v>46205</v>
+      </c>
+      <c r="B990" s="4">
+        <v>46209</v>
+      </c>
+      <c r="C990" s="5">
+        <v>8766</v>
+      </c>
+      <c r="D990" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E990" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F990" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G990" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H990" s="5">
+        <v>100</v>
+      </c>
+      <c r="I990" s="7">
+        <v>7479.9</v>
+      </c>
+      <c r="J990" s="9">
+        <v>0</v>
+      </c>
+      <c r="K990" s="9">
+        <v>0</v>
+      </c>
+      <c r="L990" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M990" s="15">
+        <f t="shared" si="21"/>
+        <v>747990</v>
+      </c>
+      <c r="N990" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="991" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A991" s="4">
+        <v>46206</v>
+      </c>
+      <c r="B991" s="4">
+        <v>46210</v>
+      </c>
+      <c r="C991" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="D991" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="E991" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F991" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G991" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H991" s="5">
+        <v>100</v>
+      </c>
+      <c r="I991" s="7">
+        <v>79080</v>
+      </c>
+      <c r="J991" s="9">
+        <v>0</v>
+      </c>
+      <c r="K991" s="9">
+        <v>0</v>
+      </c>
+      <c r="L991" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M991" s="15">
+        <f t="shared" si="21"/>
+        <v>7908000</v>
+      </c>
+      <c r="N991" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="992" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A992" s="4">
+        <v>46206</v>
+      </c>
+      <c r="B992" s="4">
+        <v>46210</v>
+      </c>
+      <c r="C992" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="D992" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="E992" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F992" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G992" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H992" s="5">
+        <v>100</v>
+      </c>
+      <c r="I992" s="7">
+        <v>81800</v>
+      </c>
+      <c r="J992" s="9">
+        <v>0</v>
+      </c>
+      <c r="K992" s="9">
+        <v>0</v>
+      </c>
+      <c r="L992" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M992" s="15">
+        <f t="shared" si="21"/>
+        <v>8180000</v>
+      </c>
+      <c r="N992" s="19">
+        <v>272000</v>
       </c>
     </row>
   </sheetData>
@@ -56864,7 +57400,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:M97"/>
+  <dimension ref="A1:M104"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.19921875" style="1" bestFit="1" customWidth="1"/>
@@ -60169,7 +60705,7 @@
         <v>100</v>
       </c>
       <c r="H87" s="19">
-        <f t="shared" ref="H87:H97" si="18">F87*G87</f>
+        <f t="shared" ref="H87:H104" si="18">F87*G87</f>
         <v>8000</v>
       </c>
       <c r="I87" s="19">
@@ -60480,11 +61016,11 @@
         <v>240</v>
       </c>
       <c r="J95" s="19">
-        <f t="shared" ref="J95:J97" si="19">H95-I95</f>
+        <f t="shared" ref="J95:J104" si="19">H95-I95</f>
         <v>945</v>
       </c>
       <c r="K95" s="19">
-        <f t="shared" ref="K95:K97" si="20">J95</f>
+        <f t="shared" ref="K95:K104" si="20">J95</f>
         <v>945</v>
       </c>
     </row>
@@ -60562,6 +61098,272 @@
       <c r="K97" s="19">
         <f t="shared" si="20"/>
         <v>7650</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A98" s="4">
+        <v>46202</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D98" s="5">
+        <v>7974</v>
+      </c>
+      <c r="E98" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="F98" s="9">
+        <v>177</v>
+      </c>
+      <c r="G98" s="5">
+        <v>100</v>
+      </c>
+      <c r="H98" s="19">
+        <f t="shared" si="18"/>
+        <v>17700</v>
+      </c>
+      <c r="I98" s="19">
+        <v>3595</v>
+      </c>
+      <c r="J98" s="19">
+        <f t="shared" si="19"/>
+        <v>14105</v>
+      </c>
+      <c r="K98" s="19">
+        <f t="shared" si="20"/>
+        <v>14105</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A99" s="4">
+        <v>46202</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D99" s="5">
+        <v>7011</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F99" s="9">
+        <v>13</v>
+      </c>
+      <c r="G99" s="5">
+        <v>500</v>
+      </c>
+      <c r="H99" s="19">
+        <f t="shared" si="18"/>
+        <v>6500</v>
+      </c>
+      <c r="I99" s="19">
+        <v>1320</v>
+      </c>
+      <c r="J99" s="19">
+        <f t="shared" si="19"/>
+        <v>5180</v>
+      </c>
+      <c r="K99" s="19">
+        <f t="shared" si="20"/>
+        <v>5180</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A100" s="4">
+        <v>46202</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D100" s="5">
+        <v>7003</v>
+      </c>
+      <c r="E100" s="9" t="s">
+        <v>444</v>
+      </c>
+      <c r="F100" s="9">
+        <v>42</v>
+      </c>
+      <c r="G100" s="5">
+        <v>100</v>
+      </c>
+      <c r="H100" s="19">
+        <f t="shared" si="18"/>
+        <v>4200</v>
+      </c>
+      <c r="I100" s="19">
+        <v>853</v>
+      </c>
+      <c r="J100" s="19">
+        <f t="shared" si="19"/>
+        <v>3347</v>
+      </c>
+      <c r="K100" s="19">
+        <f t="shared" si="20"/>
+        <v>3347</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A101" s="4">
+        <v>46202</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D101" s="5">
+        <v>5016</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="F101" s="9">
+        <v>25</v>
+      </c>
+      <c r="G101" s="5">
+        <v>100</v>
+      </c>
+      <c r="H101" s="19">
+        <f t="shared" si="18"/>
+        <v>2500</v>
+      </c>
+      <c r="I101" s="19">
+        <v>507</v>
+      </c>
+      <c r="J101" s="19">
+        <f t="shared" si="19"/>
+        <v>1993</v>
+      </c>
+      <c r="K101" s="19">
+        <f t="shared" si="20"/>
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A102" s="4">
+        <v>46202</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D102" s="5">
+        <v>4661</v>
+      </c>
+      <c r="E102" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="F102" s="9">
+        <v>8</v>
+      </c>
+      <c r="G102" s="5">
+        <v>100</v>
+      </c>
+      <c r="H102" s="19">
+        <f t="shared" si="18"/>
+        <v>800</v>
+      </c>
+      <c r="I102" s="19">
+        <v>162</v>
+      </c>
+      <c r="J102" s="19">
+        <f t="shared" si="19"/>
+        <v>638</v>
+      </c>
+      <c r="K102" s="19">
+        <f t="shared" si="20"/>
+        <v>638</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A103" s="4">
+        <v>46202</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D103" s="5">
+        <v>2201</v>
+      </c>
+      <c r="E103" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="F103" s="9">
+        <v>32.5</v>
+      </c>
+      <c r="G103" s="5">
+        <v>100</v>
+      </c>
+      <c r="H103" s="19">
+        <f t="shared" si="18"/>
+        <v>3250</v>
+      </c>
+      <c r="I103" s="19">
+        <v>659</v>
+      </c>
+      <c r="J103" s="19">
+        <f t="shared" si="19"/>
+        <v>2591</v>
+      </c>
+      <c r="K103" s="19">
+        <f t="shared" si="20"/>
+        <v>2591</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A104" s="4">
+        <v>46203</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D104" s="5">
+        <v>8766</v>
+      </c>
+      <c r="E104" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F104" s="9">
+        <v>112.5</v>
+      </c>
+      <c r="G104" s="5">
+        <v>100</v>
+      </c>
+      <c r="H104" s="19">
+        <f t="shared" si="18"/>
+        <v>11250</v>
+      </c>
+      <c r="I104" s="19">
+        <v>2284</v>
+      </c>
+      <c r="J104" s="19">
+        <f t="shared" si="19"/>
+        <v>8966</v>
+      </c>
+      <c r="K104" s="19">
+        <f t="shared" si="20"/>
+        <v>8966</v>
       </c>
     </row>
   </sheetData>
@@ -60577,7 +61379,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:AA77"/>
+  <dimension ref="A1:AA85"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="11.296875" style="1" bestFit="1" customWidth="1"/>
@@ -66318,7 +67120,7 @@
       <c r="P70" s="8">
         <v>18867</v>
       </c>
-      <c r="Q70" s="49">
+      <c r="Q70" s="4">
         <v>46091</v>
       </c>
       <c r="R70" s="7">
@@ -66401,7 +67203,7 @@
       <c r="P71" s="9">
         <v>0</v>
       </c>
-      <c r="Q71" s="9" t="s">
+      <c r="Q71" s="6" t="s">
         <v>31</v>
       </c>
       <c r="R71" s="9">
@@ -66484,7 +67286,7 @@
       <c r="P72" s="8">
         <v>39427</v>
       </c>
-      <c r="Q72" s="49">
+      <c r="Q72" s="4">
         <v>46091</v>
       </c>
       <c r="R72" s="7">
@@ -66567,7 +67369,7 @@
       <c r="P73" s="9">
         <v>0</v>
       </c>
-      <c r="Q73" s="9" t="s">
+      <c r="Q73" s="6" t="s">
         <v>31</v>
       </c>
       <c r="R73" s="9">
@@ -66650,7 +67452,7 @@
       <c r="P74" s="8">
         <v>46089</v>
       </c>
-      <c r="Q74" s="49">
+      <c r="Q74" s="4">
         <v>46091</v>
       </c>
       <c r="R74" s="7">
@@ -66733,7 +67535,7 @@
       <c r="P75" s="9">
         <v>0</v>
       </c>
-      <c r="Q75" s="9" t="s">
+      <c r="Q75" s="6" t="s">
         <v>31</v>
       </c>
       <c r="R75" s="9">
@@ -66928,6 +67730,666 @@
         <v>0</v>
       </c>
       <c r="AA77" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A78" s="4">
+        <v>46202</v>
+      </c>
+      <c r="B78" s="4">
+        <v>46204</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H78" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I78" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J78" s="5">
+        <v>100</v>
+      </c>
+      <c r="K78" s="7">
+        <v>86800</v>
+      </c>
+      <c r="L78" s="9">
+        <v>0</v>
+      </c>
+      <c r="M78" s="9">
+        <v>0</v>
+      </c>
+      <c r="N78" s="9">
+        <v>257</v>
+      </c>
+      <c r="O78" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="P78" s="20">
+        <v>-120257</v>
+      </c>
+      <c r="Q78" s="4">
+        <v>46202</v>
+      </c>
+      <c r="R78" s="7">
+        <v>85600</v>
+      </c>
+      <c r="S78" s="9">
+        <v>0</v>
+      </c>
+      <c r="T78" s="9">
+        <v>0</v>
+      </c>
+      <c r="U78" s="9">
+        <v>0</v>
+      </c>
+      <c r="V78" s="9">
+        <v>0</v>
+      </c>
+      <c r="W78" s="9">
+        <v>0</v>
+      </c>
+      <c r="X78" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="9">
+        <v>257</v>
+      </c>
+      <c r="Z78" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A79" s="4">
+        <v>46202</v>
+      </c>
+      <c r="B79" s="4">
+        <v>46204</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G79" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H79" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J79" s="5">
+        <v>100</v>
+      </c>
+      <c r="K79" s="7">
+        <v>85600</v>
+      </c>
+      <c r="L79" s="9">
+        <v>0</v>
+      </c>
+      <c r="M79" s="9">
+        <v>0</v>
+      </c>
+      <c r="N79" s="9">
+        <v>0</v>
+      </c>
+      <c r="O79" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="P79" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q79" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="R79" s="9">
+        <v>0</v>
+      </c>
+      <c r="S79" s="9">
+        <v>0</v>
+      </c>
+      <c r="T79" s="9">
+        <v>0</v>
+      </c>
+      <c r="U79" s="9">
+        <v>0</v>
+      </c>
+      <c r="V79" s="9">
+        <v>0</v>
+      </c>
+      <c r="W79" s="9">
+        <v>0</v>
+      </c>
+      <c r="X79" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A80" s="4">
+        <v>46202</v>
+      </c>
+      <c r="B80" s="4">
+        <v>46204</v>
+      </c>
+      <c r="C80" s="5">
+        <v>6857</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H80" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I80" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J80" s="5">
+        <v>100</v>
+      </c>
+      <c r="K80" s="7">
+        <v>31710</v>
+      </c>
+      <c r="L80" s="9">
+        <v>0</v>
+      </c>
+      <c r="M80" s="9">
+        <v>0</v>
+      </c>
+      <c r="N80" s="9">
+        <v>94</v>
+      </c>
+      <c r="O80" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="P80" s="20">
+        <v>-46094</v>
+      </c>
+      <c r="Q80" s="4">
+        <v>46202</v>
+      </c>
+      <c r="R80" s="7">
+        <v>31250</v>
+      </c>
+      <c r="S80" s="9">
+        <v>0</v>
+      </c>
+      <c r="T80" s="9">
+        <v>0</v>
+      </c>
+      <c r="U80" s="9">
+        <v>0</v>
+      </c>
+      <c r="V80" s="9">
+        <v>0</v>
+      </c>
+      <c r="W80" s="9">
+        <v>0</v>
+      </c>
+      <c r="X80" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="9">
+        <v>94</v>
+      </c>
+      <c r="Z80" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A81" s="4">
+        <v>46202</v>
+      </c>
+      <c r="B81" s="4">
+        <v>46204</v>
+      </c>
+      <c r="C81" s="5">
+        <v>6857</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H81" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I81" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J81" s="5">
+        <v>100</v>
+      </c>
+      <c r="K81" s="7">
+        <v>31250</v>
+      </c>
+      <c r="L81" s="9">
+        <v>0</v>
+      </c>
+      <c r="M81" s="9">
+        <v>0</v>
+      </c>
+      <c r="N81" s="9">
+        <v>0</v>
+      </c>
+      <c r="O81" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="P81" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q81" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="R81" s="9">
+        <v>0</v>
+      </c>
+      <c r="S81" s="9">
+        <v>0</v>
+      </c>
+      <c r="T81" s="9">
+        <v>0</v>
+      </c>
+      <c r="U81" s="9">
+        <v>0</v>
+      </c>
+      <c r="V81" s="9">
+        <v>0</v>
+      </c>
+      <c r="W81" s="9">
+        <v>0</v>
+      </c>
+      <c r="X81" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A82" s="4">
+        <v>46203</v>
+      </c>
+      <c r="B82" s="4">
+        <v>46205</v>
+      </c>
+      <c r="C82" s="5">
+        <v>6857</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H82" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J82" s="5">
+        <v>100</v>
+      </c>
+      <c r="K82" s="7">
+        <v>31600</v>
+      </c>
+      <c r="L82" s="9">
+        <v>0</v>
+      </c>
+      <c r="M82" s="9">
+        <v>0</v>
+      </c>
+      <c r="N82" s="9">
+        <v>0</v>
+      </c>
+      <c r="O82" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="P82" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q82" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="R82" s="9">
+        <v>0</v>
+      </c>
+      <c r="S82" s="9">
+        <v>0</v>
+      </c>
+      <c r="T82" s="9">
+        <v>0</v>
+      </c>
+      <c r="U82" s="9">
+        <v>0</v>
+      </c>
+      <c r="V82" s="9">
+        <v>0</v>
+      </c>
+      <c r="W82" s="9">
+        <v>0</v>
+      </c>
+      <c r="X82" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y82" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z82" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA82" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A83" s="4">
+        <v>46203</v>
+      </c>
+      <c r="B83" s="4">
+        <v>46205</v>
+      </c>
+      <c r="C83" s="5">
+        <v>6857</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H83" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I83" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J83" s="5">
+        <v>100</v>
+      </c>
+      <c r="K83" s="7">
+        <v>32458.9</v>
+      </c>
+      <c r="L83" s="9">
+        <v>0</v>
+      </c>
+      <c r="M83" s="9">
+        <v>0</v>
+      </c>
+      <c r="N83" s="9">
+        <v>95</v>
+      </c>
+      <c r="O83" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="P83" s="19">
+        <v>-85985</v>
+      </c>
+      <c r="Q83" s="4">
+        <v>46203</v>
+      </c>
+      <c r="R83" s="7">
+        <v>31600</v>
+      </c>
+      <c r="S83" s="9">
+        <v>0</v>
+      </c>
+      <c r="T83" s="9">
+        <v>0</v>
+      </c>
+      <c r="U83" s="9">
+        <v>0</v>
+      </c>
+      <c r="V83" s="9">
+        <v>0</v>
+      </c>
+      <c r="W83" s="9">
+        <v>0</v>
+      </c>
+      <c r="X83" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="9">
+        <v>95</v>
+      </c>
+      <c r="Z83" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA83" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A84" s="4">
+        <v>46206</v>
+      </c>
+      <c r="B84" s="4">
+        <v>46210</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H84" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J84" s="5">
+        <v>100</v>
+      </c>
+      <c r="K84" s="7">
+        <v>73960</v>
+      </c>
+      <c r="L84" s="9">
+        <v>0</v>
+      </c>
+      <c r="M84" s="9">
+        <v>0</v>
+      </c>
+      <c r="N84" s="9">
+        <v>0</v>
+      </c>
+      <c r="O84" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="P84" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q84" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="R84" s="9">
+        <v>0</v>
+      </c>
+      <c r="S84" s="9">
+        <v>0</v>
+      </c>
+      <c r="T84" s="9">
+        <v>0</v>
+      </c>
+      <c r="U84" s="9">
+        <v>0</v>
+      </c>
+      <c r="V84" s="9">
+        <v>0</v>
+      </c>
+      <c r="W84" s="9">
+        <v>0</v>
+      </c>
+      <c r="X84" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="A85" s="4">
+        <v>46206</v>
+      </c>
+      <c r="B85" s="4">
+        <v>46210</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H85" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J85" s="5">
+        <v>100</v>
+      </c>
+      <c r="K85" s="7">
+        <v>76578</v>
+      </c>
+      <c r="L85" s="9">
+        <v>0</v>
+      </c>
+      <c r="M85" s="9">
+        <v>0</v>
+      </c>
+      <c r="N85" s="9"/>
+      <c r="O85" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="P85" s="20">
+        <v>-261800</v>
+      </c>
+      <c r="Q85" s="4">
+        <v>46206</v>
+      </c>
+      <c r="R85" s="7">
+        <v>73960</v>
+      </c>
+      <c r="S85" s="9">
+        <v>0</v>
+      </c>
+      <c r="T85" s="9">
+        <v>0</v>
+      </c>
+      <c r="U85" s="9">
+        <v>0</v>
+      </c>
+      <c r="V85" s="9">
+        <v>0</v>
+      </c>
+      <c r="W85" s="9">
+        <v>0</v>
+      </c>
+      <c r="X85" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="9"/>
+      <c r="Z85" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA85" s="9">
         <v>0</v>
       </c>
     </row>

--- a/data/02_運用_rakuten.xlsx
+++ b/data/02_運用_rakuten.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6ca29965d2a6599a/01_資産管理/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="667" documentId="13_ncr:1_{F23918F6-93A0-4FFC-9C54-3B208A91E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B8B5871-07A0-49EA-B826-0AB6072A9C4B}"/>
+  <xr:revisionPtr revIDLastSave="704" documentId="13_ncr:1_{F23918F6-93A0-4FFC-9C54-3B208A91E086}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E2A60F2-C4C4-4863-97CF-2CC2EDDBA28A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="819" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="819" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="まとめ_日本" sheetId="10" r:id="rId1"/>
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">国内株式_信用!$A$1:$AA$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">国内株式_特定!$A$1:$N$963</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">国内株式_特定_配当!$A$1:$K$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">投資信託!$A$1:$K$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">投資信託!$A$1:$K$67</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">米国株式!$A$1:$S$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">米国株式_配当!$A$1:$K$74</definedName>
   </definedNames>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7673" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7751" uniqueCount="483">
   <si>
     <t>約定日</t>
   </si>
@@ -2131,6 +2131,16 @@
   <si>
     <t>京都フィナンシャルＧ</t>
   </si>
+  <si>
+    <t>サンリオ</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>278A</t>
+  </si>
+  <si>
+    <t>ＴＥＲＲＡＤＲＯＮＥ</t>
+  </si>
 </sst>
 </file>
 
@@ -2851,7 +2861,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3017,16 +3027,22 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3050,12 +3066,6 @@
     <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3067,6 +3077,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="39" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -3346,31 +3359,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="59" t="s">
         <v>213</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55" t="s">
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59" t="s">
         <v>216</v>
       </c>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
-      <c r="K1" s="55" t="s">
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
+      <c r="K1" s="59" t="s">
         <v>218</v>
       </c>
-      <c r="L1" s="55"/>
-      <c r="M1" s="55"/>
-      <c r="N1" s="55"/>
-      <c r="O1" s="63" t="s">
+      <c r="L1" s="59"/>
+      <c r="M1" s="59"/>
+      <c r="N1" s="59"/>
+      <c r="O1" s="65" t="s">
         <v>302</v>
       </c>
-      <c r="P1" s="64"/>
-      <c r="Q1" s="64"/>
-      <c r="R1" s="65"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="67"/>
       <c r="S1" s="37" t="s">
         <v>219</v>
       </c>
@@ -3382,50 +3395,50 @@
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="55" t="s">
         <v>212</v>
       </c>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57" t="s">
+      <c r="C2" s="55"/>
+      <c r="D2" s="55" t="s">
         <v>211</v>
       </c>
-      <c r="E2" s="58" t="s">
+      <c r="E2" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="55" t="s">
         <v>212</v>
       </c>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57" t="s">
+      <c r="G2" s="55"/>
+      <c r="H2" s="55" t="s">
         <v>211</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="J2" s="60" t="s">
+      <c r="J2" s="62" t="s">
         <v>217</v>
       </c>
-      <c r="K2" s="57" t="s">
+      <c r="K2" s="55" t="s">
         <v>212</v>
       </c>
-      <c r="L2" s="57"/>
-      <c r="M2" s="58" t="s">
+      <c r="L2" s="55"/>
+      <c r="M2" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="62" t="s">
         <v>217</v>
       </c>
-      <c r="O2" s="61" t="s">
+      <c r="O2" s="63" t="s">
         <v>212</v>
       </c>
-      <c r="P2" s="62"/>
-      <c r="Q2" s="58" t="s">
+      <c r="P2" s="64"/>
+      <c r="Q2" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="R2" s="60" t="s">
+      <c r="R2" s="62" t="s">
         <v>217</v>
       </c>
-      <c r="S2" s="59" t="s">
+      <c r="S2" s="61" t="s">
         <v>214</v>
       </c>
       <c r="U2" s="49">
@@ -3433,7 +3446,7 @@
       </c>
       <c r="V2" s="49">
         <f ca="1">TODAY()</f>
-        <v>46207</v>
+        <v>46222</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.45">
@@ -3443,38 +3456,38 @@
       <c r="C3" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="58"/>
       <c r="F3" s="32" t="s">
         <v>206</v>
       </c>
       <c r="G3" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="H3" s="57"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
       <c r="K3" s="32" t="s">
         <v>206</v>
       </c>
       <c r="L3" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="M3" s="58"/>
-      <c r="N3" s="58"/>
+      <c r="M3" s="57"/>
+      <c r="N3" s="57"/>
       <c r="O3" s="32" t="s">
         <v>206</v>
       </c>
       <c r="P3" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="Q3" s="58"/>
-      <c r="R3" s="58"/>
-      <c r="S3" s="59"/>
-      <c r="U3" s="55" t="s">
+      <c r="Q3" s="57"/>
+      <c r="R3" s="57"/>
+      <c r="S3" s="61"/>
+      <c r="U3" s="59" t="s">
         <v>363</v>
       </c>
-      <c r="V3" s="55"/>
+      <c r="V3" s="59"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A4" s="34" t="s">
@@ -3498,23 +3511,23 @@
       </c>
       <c r="F4" s="20">
         <f>SUM(F5:F100)</f>
-        <v>14015292</v>
+        <v>14240652</v>
       </c>
       <c r="G4" s="20">
         <f>SUM(G5:G100)</f>
-        <v>-5393677</v>
+        <v>-5416227</v>
       </c>
       <c r="H4" s="20">
         <f>SUM(H5:H100)</f>
-        <v>916435</v>
+        <v>921005</v>
       </c>
       <c r="I4" s="35">
         <f>SUM(F4:H4)</f>
-        <v>9538050</v>
+        <v>9745430</v>
       </c>
       <c r="J4" s="35">
         <f>SUM(J5:J100)</f>
-        <v>7600395.1425000001</v>
+        <v>7765645.8954999996</v>
       </c>
       <c r="K4" s="20">
         <f>SUM(K5:K100)</f>
@@ -3522,15 +3535,15 @@
       </c>
       <c r="L4" s="20">
         <f>SUM(L5:L100)</f>
-        <v>-1192189</v>
+        <v>-1192411</v>
       </c>
       <c r="M4" s="35">
         <f>SUM(K4:L4)</f>
-        <v>-717941</v>
+        <v>-718163</v>
       </c>
       <c r="N4" s="35">
         <f>SUM(N5:N100)</f>
-        <v>-719996.67485000007</v>
+        <v>-720218.67485000007</v>
       </c>
       <c r="O4" s="20">
         <f>SUM(O5:O100)</f>
@@ -3550,13 +3563,13 @@
       </c>
       <c r="S4" s="38">
         <f>SUM(E4,J4,N4,R4)</f>
-        <v>10213778.680950001</v>
-      </c>
-      <c r="U4" s="56">
+        <v>10378807.433950001</v>
+      </c>
+      <c r="U4" s="60">
         <f ca="1">(V2-U2)/365</f>
-        <v>5.6493150684931503</v>
-      </c>
-      <c r="V4" s="56"/>
+        <v>5.6904109589041099</v>
+      </c>
+      <c r="V4" s="60"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A5" s="34" t="s">
@@ -3615,11 +3628,11 @@
         <v>-68778</v>
       </c>
       <c r="O5" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2021/1/1",投資信託!$B$2:$B$1033,"&lt;=2021/12/31",投資信託!$K$2:$K$1033,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1035,投資信託!$B$2:$B$1035,"&gt;=2021/1/1",投資信託!$B$2:$B$1035,"&lt;=2021/12/31",投資信託!$K$2:$K$1035,"&gt;=0")</f>
         <v>7366</v>
       </c>
       <c r="P5" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2021/1/1",投資信託!$B$2:$B$1033,"&lt;=2021/12/31",投資信託!$K$2:$K$1033,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1035,投資信託!$B$2:$B$1035,"&gt;=2021/1/1",投資信託!$B$2:$B$1035,"&lt;=2021/12/31",投資信託!$K$2:$K$1035,"&lt;0")</f>
         <v>-1498</v>
       </c>
       <c r="Q5" s="35">
@@ -3692,11 +3705,11 @@
         <v>-106573</v>
       </c>
       <c r="O6" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2022/1/1",投資信託!$B$2:$B$1033,"&lt;=2022/12/31",投資信託!$K$2:$K$1033,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1035,投資信託!$B$2:$B$1035,"&gt;=2022/1/1",投資信託!$B$2:$B$1035,"&lt;=2022/12/31",投資信託!$K$2:$K$1035,"&gt;=0")</f>
         <v>0</v>
       </c>
       <c r="P6" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2022/1/1",投資信託!$B$2:$B$1033,"&lt;=2022/12/31",投資信託!$K$2:$K$1033,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1035,投資信託!$B$2:$B$1035,"&gt;=2022/1/1",投資信託!$B$2:$B$1035,"&lt;=2022/12/31",投資信託!$K$2:$K$1035,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="Q6" s="35">
@@ -3769,11 +3782,11 @@
         <v>-50703</v>
       </c>
       <c r="O7" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2023/1/1",投資信託!$B$2:$B$1033,"&lt;=2023/12/31",投資信託!$K$2:$K$1033,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1035,投資信託!$B$2:$B$1035,"&gt;=2023/1/1",投資信託!$B$2:$B$1035,"&lt;=2023/12/31",投資信託!$K$2:$K$1035,"&gt;=0")</f>
         <v>0</v>
       </c>
       <c r="P7" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2023/1/1",投資信託!$B$2:$B$1033,"&lt;=2023/12/31",投資信託!$K$2:$K$1033,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1035,投資信託!$B$2:$B$1035,"&gt;=2023/1/1",投資信託!$B$2:$B$1035,"&lt;=2023/12/31",投資信託!$K$2:$K$1035,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="Q7" s="35">
@@ -3846,11 +3859,11 @@
         <v>-247960</v>
       </c>
       <c r="O8" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2024/1/1",投資信託!$B$2:$B$1033,"&lt;=2024/12/31",投資信託!$K$2:$K$1033,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1035,投資信託!$B$2:$B$1035,"&gt;=2024/1/1",投資信託!$B$2:$B$1035,"&lt;=2024/12/31",投資信託!$K$2:$K$1035,"&gt;=0")</f>
         <v>0</v>
       </c>
       <c r="P8" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2024/1/1",投資信託!$B$2:$B$1033,"&lt;=2024/12/31",投資信託!$K$2:$K$1033,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1035,投資信託!$B$2:$B$1035,"&gt;=2024/1/1",投資信託!$B$2:$B$1035,"&lt;=2024/12/31",投資信託!$K$2:$K$1035,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="Q8" s="35">
@@ -3923,11 +3936,11 @@
         <v>8063.3251500000006</v>
       </c>
       <c r="O9" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2025/1/1",投資信託!$B$2:$B$1033,"&lt;=2025/12/31",投資信託!$K$2:$K$1033,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1035,投資信託!$B$2:$B$1035,"&gt;=2025/1/1",投資信託!$B$2:$B$1035,"&lt;=2025/12/31",投資信託!$K$2:$K$1035,"&gt;=0")</f>
         <v>185421</v>
       </c>
       <c r="P9" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2025/1/1",投資信託!$B$2:$B$1033,"&lt;=2025/12/31",投資信託!$K$2:$K$1033,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1035,投資信託!$B$2:$B$1035,"&gt;=2025/1/1",投資信託!$B$2:$B$1035,"&lt;=2025/12/31",投資信託!$K$2:$K$1035,"&lt;0")</f>
         <v>-1071</v>
       </c>
       <c r="Q9" s="35">
@@ -3965,23 +3978,23 @@
       </c>
       <c r="F10" s="19">
         <f>SUMIFS(国内株式_特定!$N$2:$N$996,国内株式_特定!$B$2:$B$996,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$996,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$996,"&gt;=0")</f>
-        <v>6368899</v>
+        <v>6594259</v>
       </c>
       <c r="G10" s="19">
         <f>SUMIFS(国内株式_特定!$N$2:$N$996,国内株式_特定!$B$2:$B$996,"&gt;=2026/1/1",国内株式_特定!$B$2:$B$996,"&lt;=2026/12/31",国内株式_特定!$N$2:$N$996,"&lt;0")</f>
-        <v>-1968378</v>
+        <v>-1990928</v>
       </c>
       <c r="H10" s="19">
         <f>SUMIFS(国内株式_特定_配当!$H$2:$H$999,国内株式_特定_配当!$A$2:$A$999,"&gt;=2026/1/1",国内株式_特定_配当!$A$2:$A$999,"&lt;=2026/12/31")</f>
-        <v>114280</v>
+        <v>118850</v>
       </c>
       <c r="I10" s="35">
         <f t="shared" si="11"/>
-        <v>4514801</v>
+        <v>4722181</v>
       </c>
       <c r="J10" s="36">
         <f t="shared" si="1"/>
-        <v>3597619.1768499999</v>
+        <v>3762869.92985</v>
       </c>
       <c r="K10" s="19">
         <f>SUMIFS(国内株式_信用!$P$2:$P$1000,国内株式_信用!$B$2:$B$1000,"&gt;=2026/1/1",国内株式_信用!$B$2:$B$1000,"&lt;=2026/12/31",国内株式_信用!$P$2:$P$1000,"&gt;=0")</f>
@@ -3989,22 +4002,22 @@
       </c>
       <c r="L10" s="19">
         <f>SUMIFS(国内株式_信用!$P$2:$P$1000,国内株式_信用!$B$2:$B$1000,"&gt;=2026/1/1",国内株式_信用!$B$2:$B$1000,"&lt;=2026/12/31",国内株式_信用!$P$2:$P$1000,"&lt;0")</f>
-        <v>-517946</v>
+        <v>-518168</v>
       </c>
       <c r="M10" s="35">
         <f t="shared" si="12"/>
-        <v>-254046</v>
+        <v>-254268</v>
       </c>
       <c r="N10" s="36">
         <f t="shared" si="13"/>
-        <v>-254046</v>
+        <v>-254268</v>
       </c>
       <c r="O10" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2026/1/1",投資信託!$B$2:$B$1033,"&lt;=2026/12/31",投資信託!$K$2:$K$1033,"&gt;=0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1035,投資信託!$B$2:$B$1035,"&gt;=2026/1/1",投資信託!$B$2:$B$1035,"&lt;=2026/12/31",投資信託!$K$2:$K$1035,"&gt;=0")</f>
         <v>0</v>
       </c>
       <c r="P10" s="19">
-        <f>SUMIFS(投資信託!$K$2:$K$1033,投資信託!$B$2:$B$1033,"&gt;=2026/1/1",投資信託!$B$2:$B$1033,"&lt;=2026/12/31",投資信託!$K$2:$K$1033,"&lt;0")</f>
+        <f>SUMIFS(投資信託!$K$2:$K$1035,投資信託!$B$2:$B$1035,"&gt;=2026/1/1",投資信託!$B$2:$B$1035,"&lt;=2026/12/31",投資信託!$K$2:$K$1035,"&lt;0")</f>
         <v>0</v>
       </c>
       <c r="Q10" s="35">
@@ -4017,7 +4030,7 @@
       </c>
       <c r="S10" s="38">
         <f>SUM(E10,J10,N10,R10)</f>
-        <v>3355783.1768499999</v>
+        <v>3520811.92985</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.45">
@@ -4031,11 +4044,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="F2:G2"/>
     <mergeCell ref="U3:V3"/>
     <mergeCell ref="U4:V4"/>
     <mergeCell ref="H2:H3"/>
@@ -4051,6 +4059,11 @@
     <mergeCell ref="O1:R1"/>
     <mergeCell ref="Q2:Q3"/>
     <mergeCell ref="R2:R3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F2:G2"/>
   </mergeCells>
   <phoneticPr fontId="18"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6840,49 +6853,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="59" t="s">
         <v>417</v>
       </c>
-      <c r="C1" s="55"/>
-      <c r="D1" s="55"/>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55" t="s">
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59" t="s">
         <v>416</v>
       </c>
-      <c r="G1" s="55"/>
-      <c r="H1" s="55"/>
-      <c r="I1" s="55"/>
-      <c r="J1" s="55"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
+      <c r="J1" s="59"/>
       <c r="K1" s="69" t="s">
         <v>219</v>
       </c>
       <c r="L1" s="69"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="55" t="s">
         <v>212</v>
       </c>
-      <c r="C2" s="57"/>
+      <c r="C2" s="55"/>
       <c r="D2" s="68" t="s">
         <v>418</v>
       </c>
-      <c r="E2" s="58" t="s">
+      <c r="E2" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="57" t="s">
+      <c r="F2" s="55" t="s">
         <v>212</v>
       </c>
-      <c r="G2" s="57"/>
+      <c r="G2" s="55"/>
       <c r="H2" s="68" t="s">
         <v>418</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="J2" s="60" t="s">
+      <c r="J2" s="62" t="s">
         <v>217</v>
       </c>
-      <c r="K2" s="59" t="s">
+      <c r="K2" s="61" t="s">
         <v>214</v>
       </c>
       <c r="L2" s="70" t="s">
@@ -6896,18 +6909,18 @@
       <c r="C3" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="D3" s="66"/>
-      <c r="E3" s="67"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="58"/>
       <c r="F3" s="32" t="s">
         <v>206</v>
       </c>
       <c r="G3" s="32" t="s">
         <v>207</v>
       </c>
-      <c r="H3" s="66"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="59"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="57"/>
+      <c r="J3" s="57"/>
+      <c r="K3" s="61"/>
       <c r="L3" s="71"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
@@ -12727,7 +12740,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:O992"/>
+  <dimension ref="A1:O1004"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="12.59765625" style="1" bestFit="1" customWidth="1"/>
@@ -54945,7 +54958,7 @@
         <v>31</v>
       </c>
       <c r="M938" s="15">
-        <f t="shared" ref="M938:M992" si="21">IF(G938="買付",H938*I938+SUM(J938:K938),H938*I938-SUM(J938:K938))</f>
+        <f t="shared" ref="M938:M1001" si="21">IF(G938="買付",H938*I938+SUM(J938:K938),H938*I938-SUM(J938:K938))</f>
         <v>526900</v>
       </c>
       <c r="N938" s="19">
@@ -57381,6 +57394,546 @@
       </c>
       <c r="N992" s="19">
         <v>272000</v>
+      </c>
+    </row>
+    <row r="993" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A993" s="4">
+        <v>46209</v>
+      </c>
+      <c r="B993" s="4">
+        <v>46211</v>
+      </c>
+      <c r="C993" s="5">
+        <v>6367</v>
+      </c>
+      <c r="D993" s="9" t="s">
+        <v>464</v>
+      </c>
+      <c r="E993" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F993" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G993" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H993" s="5">
+        <v>100</v>
+      </c>
+      <c r="I993" s="7">
+        <v>26000</v>
+      </c>
+      <c r="J993" s="9">
+        <v>0</v>
+      </c>
+      <c r="K993" s="9">
+        <v>0</v>
+      </c>
+      <c r="L993" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M993" s="15">
+        <f t="shared" si="21"/>
+        <v>2600000</v>
+      </c>
+      <c r="N993" s="19">
+        <v>160000</v>
+      </c>
+    </row>
+    <row r="994" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A994" s="4">
+        <v>46211</v>
+      </c>
+      <c r="B994" s="4">
+        <v>46213</v>
+      </c>
+      <c r="C994" s="5">
+        <v>5844</v>
+      </c>
+      <c r="D994" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="E994" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F994" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G994" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H994" s="5">
+        <v>200</v>
+      </c>
+      <c r="I994" s="7">
+        <v>4788</v>
+      </c>
+      <c r="J994" s="9">
+        <v>0</v>
+      </c>
+      <c r="K994" s="9">
+        <v>0</v>
+      </c>
+      <c r="L994" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M994" s="15">
+        <f t="shared" si="21"/>
+        <v>957600</v>
+      </c>
+      <c r="N994" s="19">
+        <v>42650</v>
+      </c>
+    </row>
+    <row r="995" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A995" s="4">
+        <v>46211</v>
+      </c>
+      <c r="B995" s="4">
+        <v>46213</v>
+      </c>
+      <c r="C995" s="5">
+        <v>8766</v>
+      </c>
+      <c r="D995" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E995" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F995" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G995" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H995" s="5">
+        <v>100</v>
+      </c>
+      <c r="I995" s="7">
+        <v>7707</v>
+      </c>
+      <c r="J995" s="9">
+        <v>0</v>
+      </c>
+      <c r="K995" s="9">
+        <v>0</v>
+      </c>
+      <c r="L995" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M995" s="15">
+        <f t="shared" si="21"/>
+        <v>770700</v>
+      </c>
+      <c r="N995" s="19">
+        <v>22710</v>
+      </c>
+    </row>
+    <row r="996" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A996" s="4">
+        <v>46213</v>
+      </c>
+      <c r="B996" s="4">
+        <v>46217</v>
+      </c>
+      <c r="C996" s="5">
+        <v>2201</v>
+      </c>
+      <c r="D996" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="E996" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F996" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G996" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H996" s="5">
+        <v>100</v>
+      </c>
+      <c r="I996" s="7">
+        <v>2664.5</v>
+      </c>
+      <c r="J996" s="9">
+        <v>0</v>
+      </c>
+      <c r="K996" s="9">
+        <v>0</v>
+      </c>
+      <c r="L996" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M996" s="15">
+        <f t="shared" si="21"/>
+        <v>266450</v>
+      </c>
+      <c r="N996" s="19">
+        <v>-22550</v>
+      </c>
+    </row>
+    <row r="997" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A997" s="4">
+        <v>46217</v>
+      </c>
+      <c r="B997" s="4">
+        <v>46219</v>
+      </c>
+      <c r="C997" s="5">
+        <v>3563</v>
+      </c>
+      <c r="D997" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="E997" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F997" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G997" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H997" s="5">
+        <v>100</v>
+      </c>
+      <c r="I997" s="7">
+        <v>5156</v>
+      </c>
+      <c r="J997" s="9">
+        <v>0</v>
+      </c>
+      <c r="K997" s="9">
+        <v>0</v>
+      </c>
+      <c r="L997" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M997" s="15">
+        <f t="shared" si="21"/>
+        <v>515600</v>
+      </c>
+      <c r="N997" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="998" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A998" s="4">
+        <v>46217</v>
+      </c>
+      <c r="B998" s="4">
+        <v>46219</v>
+      </c>
+      <c r="C998" s="5">
+        <v>6098</v>
+      </c>
+      <c r="D998" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="E998" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F998" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G998" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H998" s="5">
+        <v>100</v>
+      </c>
+      <c r="I998" s="7">
+        <v>12840</v>
+      </c>
+      <c r="J998" s="9">
+        <v>0</v>
+      </c>
+      <c r="K998" s="9">
+        <v>0</v>
+      </c>
+      <c r="L998" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M998" s="15">
+        <f t="shared" si="21"/>
+        <v>1284000</v>
+      </c>
+      <c r="N998" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="999" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A999" s="4">
+        <v>46217</v>
+      </c>
+      <c r="B999" s="4">
+        <v>46219</v>
+      </c>
+      <c r="C999" s="5">
+        <v>8316</v>
+      </c>
+      <c r="D999" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="E999" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F999" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G999" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H999" s="5">
+        <v>100</v>
+      </c>
+      <c r="I999" s="7">
+        <v>6945</v>
+      </c>
+      <c r="J999" s="9">
+        <v>0</v>
+      </c>
+      <c r="K999" s="9">
+        <v>0</v>
+      </c>
+      <c r="L999" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M999" s="15">
+        <f t="shared" si="21"/>
+        <v>694500</v>
+      </c>
+      <c r="N999" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A1000" s="4">
+        <v>46218</v>
+      </c>
+      <c r="B1000" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C1000" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="D1000" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="E1000" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1000" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1000" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1000" s="5">
+        <v>100</v>
+      </c>
+      <c r="I1000" s="7">
+        <v>11850</v>
+      </c>
+      <c r="J1000" s="9">
+        <v>0</v>
+      </c>
+      <c r="K1000" s="9">
+        <v>0</v>
+      </c>
+      <c r="L1000" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1000" s="15">
+        <f t="shared" si="21"/>
+        <v>1185000</v>
+      </c>
+      <c r="N1000" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A1001" s="4">
+        <v>46218</v>
+      </c>
+      <c r="B1001" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C1001" s="5">
+        <v>2802</v>
+      </c>
+      <c r="D1001" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="E1001" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1001" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1001" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1001" s="5">
+        <v>100</v>
+      </c>
+      <c r="I1001" s="7">
+        <v>5610</v>
+      </c>
+      <c r="J1001" s="9">
+        <v>0</v>
+      </c>
+      <c r="K1001" s="9">
+        <v>0</v>
+      </c>
+      <c r="L1001" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1001" s="15">
+        <f t="shared" si="21"/>
+        <v>561000</v>
+      </c>
+      <c r="N1001" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A1002" s="4">
+        <v>46218</v>
+      </c>
+      <c r="B1002" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C1002" s="5">
+        <v>3563</v>
+      </c>
+      <c r="D1002" s="9" t="s">
+        <v>370</v>
+      </c>
+      <c r="E1002" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1002" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1002" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1002" s="5">
+        <v>100</v>
+      </c>
+      <c r="I1002" s="7">
+        <v>5267.9</v>
+      </c>
+      <c r="J1002" s="9">
+        <v>0</v>
+      </c>
+      <c r="K1002" s="9">
+        <v>0</v>
+      </c>
+      <c r="L1002" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M1002" s="15">
+        <f t="shared" ref="M1002:M1004" si="22">IF(G1002="買付",H1002*I1002+SUM(J1002:K1002),H1002*I1002-SUM(J1002:K1002))</f>
+        <v>526790</v>
+      </c>
+      <c r="N1002" s="19">
+        <v>11190</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A1003" s="4">
+        <v>46218</v>
+      </c>
+      <c r="B1003" s="4">
+        <v>46220</v>
+      </c>
+      <c r="C1003" s="5">
+        <v>6857</v>
+      </c>
+      <c r="D1003" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="E1003" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1003" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1003" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1003" s="5">
+        <v>100</v>
+      </c>
+      <c r="I1003" s="7">
+        <v>31298</v>
+      </c>
+      <c r="J1003" s="9">
+        <v>0</v>
+      </c>
+      <c r="K1003" s="9">
+        <v>0</v>
+      </c>
+      <c r="L1003" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="M1003" s="15">
+        <f t="shared" si="22"/>
+        <v>3129800</v>
+      </c>
+      <c r="N1003" s="19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="A1004" s="4">
+        <v>46219</v>
+      </c>
+      <c r="B1004" s="4">
+        <v>46224</v>
+      </c>
+      <c r="C1004" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="D1004" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="E1004" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1004" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1004" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1004" s="5">
+        <v>100</v>
+      </c>
+      <c r="I1004" s="7">
+        <v>12290</v>
+      </c>
+      <c r="J1004" s="9">
+        <v>0</v>
+      </c>
+      <c r="K1004" s="9">
+        <v>0</v>
+      </c>
+      <c r="L1004" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="M1004" s="15">
+        <f t="shared" si="22"/>
+        <v>1229000</v>
+      </c>
+      <c r="N1004" s="19">
+        <v>44000</v>
       </c>
     </row>
   </sheetData>
@@ -57400,7 +57953,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:M104"/>
+  <dimension ref="A1:M106"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.19921875" style="1" bestFit="1" customWidth="1"/>
@@ -60705,7 +61258,7 @@
         <v>100</v>
       </c>
       <c r="H87" s="19">
-        <f t="shared" ref="H87:H104" si="18">F87*G87</f>
+        <f t="shared" ref="H87:H106" si="18">F87*G87</f>
         <v>8000</v>
       </c>
       <c r="I87" s="19">
@@ -61016,11 +61569,11 @@
         <v>240</v>
       </c>
       <c r="J95" s="19">
-        <f t="shared" ref="J95:J104" si="19">H95-I95</f>
+        <f t="shared" ref="J95:J106" si="19">H95-I95</f>
         <v>945</v>
       </c>
       <c r="K95" s="19">
-        <f t="shared" ref="K95:K104" si="20">J95</f>
+        <f t="shared" ref="K95:K106" si="20">J95</f>
         <v>945</v>
       </c>
     </row>
@@ -61364,6 +61917,82 @@
       <c r="K104" s="19">
         <f t="shared" si="20"/>
         <v>8966</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A105" s="4">
+        <v>46216</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D105" s="5">
+        <v>1488</v>
+      </c>
+      <c r="E105" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="F105" s="72">
+        <v>14</v>
+      </c>
+      <c r="G105" s="5">
+        <v>55</v>
+      </c>
+      <c r="H105" s="19">
+        <f t="shared" si="18"/>
+        <v>770</v>
+      </c>
+      <c r="I105" s="19">
+        <v>155</v>
+      </c>
+      <c r="J105" s="19">
+        <f t="shared" si="19"/>
+        <v>615</v>
+      </c>
+      <c r="K105" s="19">
+        <f t="shared" si="20"/>
+        <v>615</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A106" s="4">
+        <v>46224</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D106" s="5">
+        <v>8136</v>
+      </c>
+      <c r="E106" s="72" t="s">
+        <v>480</v>
+      </c>
+      <c r="F106" s="72">
+        <v>38</v>
+      </c>
+      <c r="G106" s="5">
+        <v>100</v>
+      </c>
+      <c r="H106" s="19">
+        <f t="shared" si="18"/>
+        <v>3800</v>
+      </c>
+      <c r="I106" s="19">
+        <v>771</v>
+      </c>
+      <c r="J106" s="19">
+        <f t="shared" si="19"/>
+        <v>3029</v>
+      </c>
+      <c r="K106" s="19">
+        <f t="shared" si="20"/>
+        <v>3029</v>
       </c>
     </row>
   </sheetData>
@@ -68354,12 +68983,14 @@
       <c r="M85" s="9">
         <v>0</v>
       </c>
-      <c r="N85" s="9"/>
+      <c r="N85" s="9">
+        <v>222</v>
+      </c>
       <c r="O85" s="9" t="s">
         <v>90</v>
       </c>
       <c r="P85" s="20">
-        <v>-261800</v>
+        <v>-262022</v>
       </c>
       <c r="Q85" s="4">
         <v>46206</v>
@@ -68385,7 +69016,9 @@
       <c r="X85" s="9">
         <v>0</v>
       </c>
-      <c r="Y85" s="9"/>
+      <c r="Y85" s="9">
+        <v>222</v>
+      </c>
       <c r="Z85" s="9">
         <v>0</v>
       </c>
@@ -68406,7 +69039,7 @@
   <sheetPr>
     <tabColor theme="2"/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K77"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="11.296875" style="1" bestFit="1" customWidth="1"/>
@@ -69435,13 +70068,13 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30" s="4">
-        <v>46128</v>
+        <v>46217</v>
       </c>
       <c r="B30" s="4">
-        <v>45950</v>
+        <v>46224</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>377</v>
+        <v>282</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>159</v>
@@ -69456,13 +70089,13 @@
         <v>284</v>
       </c>
       <c r="H30" s="21">
-        <v>40242</v>
+        <v>7854</v>
       </c>
       <c r="I30" s="21">
-        <v>17395</v>
+        <v>38197</v>
       </c>
       <c r="J30" s="21">
-        <v>70000</v>
+        <v>30000</v>
       </c>
       <c r="K30" s="21">
         <v>0</v>
@@ -69470,10 +70103,10 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31" s="4">
-        <v>45974</v>
+        <v>46128</v>
       </c>
       <c r="B31" s="4">
-        <v>45979</v>
+        <v>45950</v>
       </c>
       <c r="C31" s="9" t="s">
         <v>377</v>
@@ -69491,10 +70124,10 @@
         <v>284</v>
       </c>
       <c r="H31" s="21">
-        <v>38038</v>
+        <v>40242</v>
       </c>
       <c r="I31" s="21">
-        <v>18403</v>
+        <v>17395</v>
       </c>
       <c r="J31" s="21">
         <v>70000</v>
@@ -69505,10 +70138,10 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A32" s="4">
-        <v>46006</v>
+        <v>45974</v>
       </c>
       <c r="B32" s="4">
-        <v>46009</v>
+        <v>45979</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>377</v>
@@ -69526,10 +70159,10 @@
         <v>284</v>
       </c>
       <c r="H32" s="21">
-        <v>37910</v>
+        <v>38038</v>
       </c>
       <c r="I32" s="21">
-        <v>18465</v>
+        <v>18403</v>
       </c>
       <c r="J32" s="21">
         <v>70000</v>
@@ -69540,10 +70173,10 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33" s="4">
-        <v>46036</v>
+        <v>46006</v>
       </c>
       <c r="B33" s="4">
-        <v>46041</v>
+        <v>46009</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>377</v>
@@ -69561,10 +70194,10 @@
         <v>284</v>
       </c>
       <c r="H33" s="21">
-        <v>35338</v>
+        <v>37910</v>
       </c>
       <c r="I33" s="21">
-        <v>19809</v>
+        <v>18465</v>
       </c>
       <c r="J33" s="21">
         <v>70000</v>
@@ -69575,10 +70208,10 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34" s="4">
-        <v>46066</v>
+        <v>46036</v>
       </c>
       <c r="B34" s="4">
-        <v>46071</v>
+        <v>46041</v>
       </c>
       <c r="C34" s="9" t="s">
         <v>377</v>
@@ -69596,10 +70229,10 @@
         <v>284</v>
       </c>
       <c r="H34" s="21">
-        <v>34978</v>
+        <v>35338</v>
       </c>
       <c r="I34" s="21">
-        <v>20013</v>
+        <v>19809</v>
       </c>
       <c r="J34" s="21">
         <v>70000</v>
@@ -69610,10 +70243,10 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35" s="4">
-        <v>46094</v>
+        <v>46066</v>
       </c>
       <c r="B35" s="4">
-        <v>46099</v>
+        <v>46071</v>
       </c>
       <c r="C35" s="9" t="s">
         <v>377</v>
@@ -69631,10 +70264,10 @@
         <v>284</v>
       </c>
       <c r="H35" s="21">
-        <v>35624</v>
+        <v>34978</v>
       </c>
       <c r="I35" s="21">
-        <v>19650</v>
+        <v>20013</v>
       </c>
       <c r="J35" s="21">
         <v>70000</v>
@@ -69645,10 +70278,10 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A36" s="4">
-        <v>46126</v>
+        <v>46094</v>
       </c>
       <c r="B36" s="4">
-        <v>46129</v>
+        <v>46099</v>
       </c>
       <c r="C36" s="9" t="s">
         <v>377</v>
@@ -69666,10 +70299,10 @@
         <v>284</v>
       </c>
       <c r="H36" s="21">
-        <v>33669</v>
+        <v>35624</v>
       </c>
       <c r="I36" s="21">
-        <v>20791</v>
+        <v>19650</v>
       </c>
       <c r="J36" s="21">
         <v>70000</v>
@@ -69680,10 +70313,10 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A37" s="4">
-        <v>46155</v>
+        <v>46126</v>
       </c>
       <c r="B37" s="4">
-        <v>46160</v>
+        <v>46129</v>
       </c>
       <c r="C37" s="9" t="s">
         <v>377</v>
@@ -69701,10 +70334,10 @@
         <v>284</v>
       </c>
       <c r="H37" s="21">
-        <v>32999</v>
+        <v>33669</v>
       </c>
       <c r="I37" s="21">
-        <v>21213</v>
+        <v>20791</v>
       </c>
       <c r="J37" s="21">
         <v>70000</v>
@@ -69715,10 +70348,10 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A38" s="4">
-        <v>46188</v>
+        <v>46155</v>
       </c>
       <c r="B38" s="4">
-        <v>46191</v>
+        <v>46160</v>
       </c>
       <c r="C38" s="9" t="s">
         <v>377</v>
@@ -69736,10 +70369,10 @@
         <v>284</v>
       </c>
       <c r="H38" s="21">
-        <v>31937</v>
+        <v>32999</v>
       </c>
       <c r="I38" s="21">
-        <v>21918</v>
+        <v>21213</v>
       </c>
       <c r="J38" s="21">
         <v>70000</v>
@@ -69750,34 +70383,34 @@
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A39" s="4">
-        <v>44368</v>
+        <v>46188</v>
       </c>
       <c r="B39" s="4">
-        <v>44371</v>
+        <v>46191</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>163</v>
+        <v>377</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G39" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H39" s="8">
-        <v>21735</v>
-      </c>
-      <c r="I39" s="8">
-        <v>13803</v>
-      </c>
-      <c r="J39" s="8">
-        <v>30000</v>
+        <v>284</v>
+      </c>
+      <c r="H39" s="21">
+        <v>31937</v>
+      </c>
+      <c r="I39" s="21">
+        <v>21918</v>
+      </c>
+      <c r="J39" s="21">
+        <v>70000</v>
       </c>
       <c r="K39" s="21">
         <v>0</v>
@@ -69785,34 +70418,34 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A40" s="4">
-        <v>44377</v>
+        <v>46217</v>
       </c>
       <c r="B40" s="4">
-        <v>44382</v>
+        <v>46220</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>163</v>
+        <v>377</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>30</v>
       </c>
       <c r="G40" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H40" s="8">
-        <v>7034</v>
-      </c>
-      <c r="I40" s="8">
-        <v>14217</v>
-      </c>
-      <c r="J40" s="8">
-        <v>10000</v>
+        <v>284</v>
+      </c>
+      <c r="H40" s="21">
+        <v>32132</v>
+      </c>
+      <c r="I40" s="21">
+        <v>21785</v>
+      </c>
+      <c r="J40" s="21">
+        <v>70000</v>
       </c>
       <c r="K40" s="21">
         <v>0</v>
@@ -69820,10 +70453,10 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A41" s="4">
-        <v>44529</v>
+        <v>44368</v>
       </c>
       <c r="B41" s="4">
-        <v>44532</v>
+        <v>44371</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>163</v>
@@ -69835,28 +70468,30 @@
         <v>295</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G41" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="H41" s="8">
-        <v>28769</v>
+        <v>21735</v>
       </c>
       <c r="I41" s="8">
-        <v>13383</v>
+        <v>13803</v>
       </c>
       <c r="J41" s="8">
-        <v>38502</v>
-      </c>
-      <c r="K41" s="19">
-        <v>-1498</v>
+        <v>30000</v>
+      </c>
+      <c r="K41" s="21">
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A42" s="4">
-        <v>44403</v>
+        <v>44377</v>
       </c>
       <c r="B42" s="4">
-        <v>44406</v>
+        <v>44382</v>
       </c>
       <c r="C42" s="9" t="s">
         <v>163</v>
@@ -69865,7 +70500,7 @@
         <v>159</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>30</v>
@@ -69874,10 +70509,10 @@
         <v>160</v>
       </c>
       <c r="H42" s="8">
-        <v>7310</v>
+        <v>7034</v>
       </c>
       <c r="I42" s="8">
-        <v>13681</v>
+        <v>14217</v>
       </c>
       <c r="J42" s="8">
         <v>10000</v>
@@ -69888,10 +70523,10 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43" s="4">
-        <v>44525</v>
+        <v>44529</v>
       </c>
       <c r="B43" s="4">
-        <v>44530</v>
+        <v>44532</v>
       </c>
       <c r="C43" s="9" t="s">
         <v>163</v>
@@ -69900,40 +70535,40 @@
         <v>159</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>298</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="8">
-        <v>7310</v>
+        <v>28769</v>
       </c>
       <c r="I43" s="8">
-        <v>13973</v>
+        <v>13383</v>
       </c>
       <c r="J43" s="8">
-        <v>10214</v>
+        <v>38502</v>
       </c>
       <c r="K43" s="19">
-        <v>214</v>
+        <v>-1498</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44" s="4">
-        <v>44165</v>
+        <v>44403</v>
       </c>
       <c r="B44" s="4">
-        <v>44168</v>
+        <v>44406</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>295</v>
+        <v>67</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>30</v>
@@ -69942,13 +70577,13 @@
         <v>160</v>
       </c>
       <c r="H44" s="8">
-        <v>3846</v>
+        <v>7310</v>
       </c>
       <c r="I44" s="8">
-        <v>13000</v>
+        <v>13681</v>
       </c>
       <c r="J44" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K44" s="21">
         <v>0</v>
@@ -69956,45 +70591,43 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A45" s="4">
-        <v>44201</v>
+        <v>44525</v>
       </c>
       <c r="B45" s="4">
-        <v>44204</v>
+        <v>44530</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>295</v>
+        <v>67</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G45" s="5" t="s">
-        <v>160</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="G45" s="5"/>
       <c r="H45" s="8">
-        <v>7604</v>
+        <v>7310</v>
       </c>
       <c r="I45" s="8">
-        <v>13152</v>
+        <v>13973</v>
       </c>
       <c r="J45" s="8">
-        <v>10000</v>
-      </c>
-      <c r="K45" s="21">
-        <v>0</v>
+        <v>10214</v>
+      </c>
+      <c r="K45" s="19">
+        <v>214</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A46" s="4">
-        <v>44236</v>
+        <v>44165</v>
       </c>
       <c r="B46" s="4">
-        <v>44242</v>
+        <v>44168</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>158</v>
@@ -70012,13 +70645,13 @@
         <v>160</v>
       </c>
       <c r="H46" s="8">
-        <v>7041</v>
+        <v>3846</v>
       </c>
       <c r="I46" s="8">
-        <v>14202</v>
+        <v>13000</v>
       </c>
       <c r="J46" s="8">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K46" s="21">
         <v>0</v>
@@ -70026,10 +70659,10 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A47" s="4">
-        <v>44257</v>
+        <v>44201</v>
       </c>
       <c r="B47" s="4">
-        <v>44260</v>
+        <v>44204</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>158</v>
@@ -70047,10 +70680,10 @@
         <v>160</v>
       </c>
       <c r="H47" s="8">
-        <v>6947</v>
+        <v>7604</v>
       </c>
       <c r="I47" s="8">
-        <v>14394</v>
+        <v>13152</v>
       </c>
       <c r="J47" s="8">
         <v>10000</v>
@@ -70061,10 +70694,10 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A48" s="4">
-        <v>44295</v>
+        <v>44236</v>
       </c>
       <c r="B48" s="4">
-        <v>44300</v>
+        <v>44242</v>
       </c>
       <c r="C48" s="9" t="s">
         <v>158</v>
@@ -70082,10 +70715,10 @@
         <v>160</v>
       </c>
       <c r="H48" s="8">
-        <v>6460</v>
+        <v>7041</v>
       </c>
       <c r="I48" s="8">
-        <v>15481</v>
+        <v>14202</v>
       </c>
       <c r="J48" s="8">
         <v>10000</v>
@@ -70096,10 +70729,10 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A49" s="4">
-        <v>44327</v>
+        <v>44257</v>
       </c>
       <c r="B49" s="4">
-        <v>44330</v>
+        <v>44260</v>
       </c>
       <c r="C49" s="9" t="s">
         <v>158</v>
@@ -70117,13 +70750,13 @@
         <v>160</v>
       </c>
       <c r="H49" s="8">
-        <v>3167</v>
+        <v>6947</v>
       </c>
       <c r="I49" s="8">
-        <v>15789</v>
+        <v>14394</v>
       </c>
       <c r="J49" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K49" s="21">
         <v>0</v>
@@ -70131,10 +70764,10 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A50" s="4">
-        <v>44350</v>
+        <v>44295</v>
       </c>
       <c r="B50" s="4">
-        <v>44355</v>
+        <v>44300</v>
       </c>
       <c r="C50" s="9" t="s">
         <v>158</v>
@@ -70152,10 +70785,10 @@
         <v>160</v>
       </c>
       <c r="H50" s="8">
-        <v>6263</v>
+        <v>6460</v>
       </c>
       <c r="I50" s="8">
-        <v>15967</v>
+        <v>15481</v>
       </c>
       <c r="J50" s="8">
         <v>10000</v>
@@ -70166,10 +70799,10 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A51" s="4">
-        <v>44377</v>
+        <v>44327</v>
       </c>
       <c r="B51" s="4">
-        <v>44382</v>
+        <v>44330</v>
       </c>
       <c r="C51" s="9" t="s">
         <v>158</v>
@@ -70187,13 +70820,13 @@
         <v>160</v>
       </c>
       <c r="H51" s="8">
-        <v>6081</v>
+        <v>3167</v>
       </c>
       <c r="I51" s="8">
-        <v>16444</v>
+        <v>15789</v>
       </c>
       <c r="J51" s="8">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K51" s="21">
         <v>0</v>
@@ -70201,10 +70834,10 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A52" s="4">
-        <v>44921</v>
+        <v>44350</v>
       </c>
       <c r="B52" s="4">
-        <v>44924</v>
+        <v>44355</v>
       </c>
       <c r="C52" s="9" t="s">
         <v>158</v>
@@ -70222,13 +70855,13 @@
         <v>160</v>
       </c>
       <c r="H52" s="8">
-        <v>24940</v>
+        <v>6263</v>
       </c>
       <c r="I52" s="8">
-        <v>17961</v>
+        <v>15967</v>
       </c>
       <c r="J52" s="8">
-        <v>44794</v>
+        <v>10000</v>
       </c>
       <c r="K52" s="21">
         <v>0</v>
@@ -70236,10 +70869,10 @@
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A53" s="4">
-        <v>45243</v>
+        <v>44377</v>
       </c>
       <c r="B53" s="4">
-        <v>45246</v>
+        <v>44382</v>
       </c>
       <c r="C53" s="9" t="s">
         <v>158</v>
@@ -70257,13 +70890,13 @@
         <v>160</v>
       </c>
       <c r="H53" s="8">
-        <v>590</v>
+        <v>6081</v>
       </c>
       <c r="I53" s="8">
-        <v>23925</v>
+        <v>16444</v>
       </c>
       <c r="J53" s="8">
-        <v>1410</v>
+        <v>10000</v>
       </c>
       <c r="K53" s="21">
         <v>0</v>
@@ -70271,10 +70904,10 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A54" s="4">
-        <v>45656</v>
+        <v>44921</v>
       </c>
       <c r="B54" s="4">
-        <v>45663</v>
+        <v>44924</v>
       </c>
       <c r="C54" s="9" t="s">
         <v>158</v>
@@ -70286,15 +70919,19 @@
         <v>295</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="G54" s="5"/>
-      <c r="H54" s="21">
-        <v>3846</v>
-      </c>
-      <c r="I54" s="9"/>
-      <c r="J54" s="9">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H54" s="8">
+        <v>24940</v>
+      </c>
+      <c r="I54" s="8">
+        <v>17961</v>
+      </c>
+      <c r="J54" s="8">
+        <v>44794</v>
       </c>
       <c r="K54" s="21">
         <v>0</v>
@@ -70302,10 +70939,10 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A55" s="4">
-        <v>45772</v>
+        <v>45243</v>
       </c>
       <c r="B55" s="4">
-        <v>45778</v>
+        <v>45246</v>
       </c>
       <c r="C55" s="9" t="s">
         <v>158</v>
@@ -70317,28 +70954,30 @@
         <v>295</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G55" s="5"/>
-      <c r="H55" s="21">
-        <v>69093</v>
-      </c>
-      <c r="I55" s="19">
-        <v>28502</v>
-      </c>
-      <c r="J55" s="19">
-        <v>196929</v>
+        <v>30</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H55" s="8">
+        <v>590</v>
+      </c>
+      <c r="I55" s="8">
+        <v>23925</v>
+      </c>
+      <c r="J55" s="8">
+        <v>1410</v>
       </c>
       <c r="K55" s="21">
-        <v>86850</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A56" s="4">
-        <v>44404</v>
+        <v>45656</v>
       </c>
       <c r="B56" s="4">
-        <v>44407</v>
+        <v>45663</v>
       </c>
       <c r="C56" s="9" t="s">
         <v>158</v>
@@ -70347,22 +70986,18 @@
         <v>159</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G56" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H56" s="8">
-        <v>11832</v>
-      </c>
-      <c r="I56" s="8">
-        <v>16903</v>
-      </c>
-      <c r="J56" s="8">
-        <v>20000</v>
+        <v>289</v>
+      </c>
+      <c r="G56" s="5"/>
+      <c r="H56" s="21">
+        <v>3846</v>
+      </c>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9">
+        <v>0</v>
       </c>
       <c r="K56" s="21">
         <v>0</v>
@@ -70370,10 +71005,10 @@
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A57" s="4">
-        <v>44435</v>
+        <v>45772</v>
       </c>
       <c r="B57" s="4">
-        <v>44440</v>
+        <v>45778</v>
       </c>
       <c r="C57" s="9" t="s">
         <v>158</v>
@@ -70382,31 +71017,31 @@
         <v>159</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>298</v>
       </c>
       <c r="G57" s="5"/>
-      <c r="H57" s="8">
-        <v>11832</v>
-      </c>
-      <c r="I57" s="8">
-        <v>17067</v>
-      </c>
-      <c r="J57" s="8">
-        <v>20194</v>
-      </c>
-      <c r="K57" s="19">
-        <v>194</v>
+      <c r="H57" s="21">
+        <v>69093</v>
+      </c>
+      <c r="I57" s="19">
+        <v>28502</v>
+      </c>
+      <c r="J57" s="19">
+        <v>196929</v>
+      </c>
+      <c r="K57" s="21">
+        <v>86850</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A58" s="4">
-        <v>45656</v>
+        <v>44404</v>
       </c>
       <c r="B58" s="4">
-        <v>45663</v>
+        <v>44407</v>
       </c>
       <c r="C58" s="9" t="s">
         <v>158</v>
@@ -70415,18 +71050,22 @@
         <v>159</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>294</v>
+        <v>67</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="G58" s="5"/>
-      <c r="H58" s="21">
-        <v>3846</v>
-      </c>
-      <c r="I58" s="9"/>
-      <c r="J58" s="9">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H58" s="8">
+        <v>11832</v>
+      </c>
+      <c r="I58" s="8">
+        <v>16903</v>
+      </c>
+      <c r="J58" s="8">
+        <v>20000</v>
       </c>
       <c r="K58" s="21">
         <v>0</v>
@@ -70434,10 +71073,10 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A59" s="4">
-        <v>45824</v>
+        <v>44435</v>
       </c>
       <c r="B59" s="4">
-        <v>45827</v>
+        <v>44440</v>
       </c>
       <c r="C59" s="9" t="s">
         <v>158</v>
@@ -70446,55 +71085,51 @@
         <v>159</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>298</v>
       </c>
       <c r="G59" s="5"/>
-      <c r="H59" s="21">
-        <v>3846</v>
-      </c>
-      <c r="I59" s="19">
-        <v>31398</v>
-      </c>
-      <c r="J59" s="19">
-        <v>12076</v>
-      </c>
-      <c r="K59" s="21">
-        <v>-1071</v>
+      <c r="H59" s="8">
+        <v>11832</v>
+      </c>
+      <c r="I59" s="8">
+        <v>17067</v>
+      </c>
+      <c r="J59" s="8">
+        <v>20194</v>
+      </c>
+      <c r="K59" s="19">
+        <v>194</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A60" s="4">
-        <v>44188</v>
+        <v>45656</v>
       </c>
       <c r="B60" s="4">
-        <v>44193</v>
+        <v>45663</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G60" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H60" s="8">
-        <v>4490</v>
-      </c>
-      <c r="I60" s="8">
-        <v>22273</v>
-      </c>
-      <c r="J60" s="8">
-        <v>10000</v>
+        <v>296</v>
+      </c>
+      <c r="G60" s="5"/>
+      <c r="H60" s="21">
+        <v>3846</v>
+      </c>
+      <c r="I60" s="9"/>
+      <c r="J60" s="9">
+        <v>0</v>
       </c>
       <c r="K60" s="21">
         <v>0</v>
@@ -70502,45 +71137,43 @@
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A61" s="4">
-        <v>44224</v>
+        <v>45824</v>
       </c>
       <c r="B61" s="4">
-        <v>44229</v>
+        <v>45827</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>295</v>
+        <v>68</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G61" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="H61" s="8">
-        <v>2108</v>
-      </c>
-      <c r="I61" s="8">
-        <v>23721</v>
-      </c>
-      <c r="J61" s="8">
-        <v>5000</v>
+        <v>298</v>
+      </c>
+      <c r="G61" s="5"/>
+      <c r="H61" s="21">
+        <v>3846</v>
+      </c>
+      <c r="I61" s="19">
+        <v>31398</v>
+      </c>
+      <c r="J61" s="19">
+        <v>12076</v>
       </c>
       <c r="K61" s="21">
-        <v>0</v>
+        <v>-1071</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A62" s="4">
-        <v>44257</v>
+        <v>44188</v>
       </c>
       <c r="B62" s="4">
-        <v>44260</v>
+        <v>44193</v>
       </c>
       <c r="C62" s="9" t="s">
         <v>162</v>
@@ -70558,13 +71191,13 @@
         <v>160</v>
       </c>
       <c r="H62" s="8">
-        <v>1938</v>
+        <v>4490</v>
       </c>
       <c r="I62" s="8">
-        <v>25804</v>
+        <v>22273</v>
       </c>
       <c r="J62" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K62" s="21">
         <v>0</v>
@@ -70572,10 +71205,10 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A63" s="4">
-        <v>44295</v>
+        <v>44224</v>
       </c>
       <c r="B63" s="4">
-        <v>44300</v>
+        <v>44229</v>
       </c>
       <c r="C63" s="9" t="s">
         <v>162</v>
@@ -70593,10 +71226,10 @@
         <v>160</v>
       </c>
       <c r="H63" s="8">
-        <v>1920</v>
+        <v>2108</v>
       </c>
       <c r="I63" s="8">
-        <v>26043</v>
+        <v>23721</v>
       </c>
       <c r="J63" s="8">
         <v>5000</v>
@@ -70607,10 +71240,10 @@
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A64" s="4">
-        <v>44327</v>
+        <v>44257</v>
       </c>
       <c r="B64" s="4">
-        <v>44330</v>
+        <v>44260</v>
       </c>
       <c r="C64" s="9" t="s">
         <v>162</v>
@@ -70628,13 +71261,13 @@
         <v>160</v>
       </c>
       <c r="H64" s="8">
-        <v>4166</v>
+        <v>1938</v>
       </c>
       <c r="I64" s="8">
-        <v>24007</v>
+        <v>25804</v>
       </c>
       <c r="J64" s="8">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="K64" s="21">
         <v>0</v>
@@ -70642,10 +71275,10 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A65" s="4">
-        <v>44350</v>
+        <v>44295</v>
       </c>
       <c r="B65" s="4">
-        <v>44355</v>
+        <v>44300</v>
       </c>
       <c r="C65" s="9" t="s">
         <v>162</v>
@@ -70663,10 +71296,10 @@
         <v>160</v>
       </c>
       <c r="H65" s="8">
-        <v>1983</v>
+        <v>1920</v>
       </c>
       <c r="I65" s="8">
-        <v>25216</v>
+        <v>26043</v>
       </c>
       <c r="J65" s="8">
         <v>5000</v>
@@ -70677,10 +71310,10 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A66" s="4">
-        <v>44362</v>
+        <v>44327</v>
       </c>
       <c r="B66" s="4">
-        <v>44365</v>
+        <v>44330</v>
       </c>
       <c r="C66" s="9" t="s">
         <v>162</v>
@@ -70692,31 +71325,33 @@
         <v>295</v>
       </c>
       <c r="F66" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G66" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="H66" s="8">
-        <v>16605</v>
+        <v>4166</v>
       </c>
       <c r="I66" s="8">
-        <v>26019</v>
+        <v>24007</v>
       </c>
       <c r="J66" s="8">
-        <v>43205</v>
-      </c>
-      <c r="K66" s="19">
-        <v>3205</v>
+        <v>10000</v>
+      </c>
+      <c r="K66" s="21">
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A67" s="4">
-        <v>44187</v>
+        <v>44350</v>
       </c>
       <c r="B67" s="4">
-        <v>44190</v>
+        <v>44355</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>159</v>
@@ -70731,27 +71366,27 @@
         <v>160</v>
       </c>
       <c r="H67" s="8">
-        <v>6447</v>
+        <v>1983</v>
       </c>
       <c r="I67" s="8">
-        <v>15511</v>
+        <v>25216</v>
       </c>
       <c r="J67" s="8">
-        <v>10000</v>
-      </c>
-      <c r="K67" s="19">
+        <v>5000</v>
+      </c>
+      <c r="K67" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A68" s="4">
-        <v>44224</v>
+        <v>44362</v>
       </c>
       <c r="B68" s="4">
-        <v>44229</v>
+        <v>44365</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>159</v>
@@ -70760,30 +71395,28 @@
         <v>295</v>
       </c>
       <c r="F68" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="G68" s="5" t="s">
-        <v>160</v>
-      </c>
+        <v>298</v>
+      </c>
+      <c r="G68" s="5"/>
       <c r="H68" s="8">
-        <v>3093</v>
+        <v>16605</v>
       </c>
       <c r="I68" s="8">
-        <v>16167</v>
+        <v>26019</v>
       </c>
       <c r="J68" s="8">
-        <v>5000</v>
+        <v>43205</v>
       </c>
       <c r="K68" s="19">
-        <v>0</v>
+        <v>3205</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A69" s="4">
-        <v>44257</v>
+        <v>44187</v>
       </c>
       <c r="B69" s="4">
-        <v>44260</v>
+        <v>44190</v>
       </c>
       <c r="C69" s="9" t="s">
         <v>161</v>
@@ -70801,13 +71434,13 @@
         <v>160</v>
       </c>
       <c r="H69" s="8">
-        <v>2978</v>
+        <v>6447</v>
       </c>
       <c r="I69" s="8">
-        <v>16792</v>
+        <v>15511</v>
       </c>
       <c r="J69" s="8">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="K69" s="19">
         <v>0</v>
@@ -70815,10 +71448,10 @@
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A70" s="4">
-        <v>44295</v>
+        <v>44224</v>
       </c>
       <c r="B70" s="4">
-        <v>44300</v>
+        <v>44229</v>
       </c>
       <c r="C70" s="9" t="s">
         <v>161</v>
@@ -70836,10 +71469,10 @@
         <v>160</v>
       </c>
       <c r="H70" s="8">
-        <v>2810</v>
+        <v>3093</v>
       </c>
       <c r="I70" s="8">
-        <v>17792</v>
+        <v>16167</v>
       </c>
       <c r="J70" s="8">
         <v>5000</v>
@@ -70850,10 +71483,10 @@
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A71" s="4">
-        <v>44327</v>
+        <v>44257</v>
       </c>
       <c r="B71" s="4">
-        <v>44330</v>
+        <v>44260</v>
       </c>
       <c r="C71" s="9" t="s">
         <v>161</v>
@@ -70871,10 +71504,10 @@
         <v>160</v>
       </c>
       <c r="H71" s="8">
-        <v>2903</v>
+        <v>2978</v>
       </c>
       <c r="I71" s="8">
-        <v>17225</v>
+        <v>16792</v>
       </c>
       <c r="J71" s="8">
         <v>5000</v>
@@ -70885,10 +71518,10 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A72" s="4">
-        <v>44350</v>
+        <v>44295</v>
       </c>
       <c r="B72" s="4">
-        <v>44355</v>
+        <v>44300</v>
       </c>
       <c r="C72" s="9" t="s">
         <v>161</v>
@@ -70906,10 +71539,10 @@
         <v>160</v>
       </c>
       <c r="H72" s="8">
-        <v>2819</v>
+        <v>2810</v>
       </c>
       <c r="I72" s="8">
-        <v>17736</v>
+        <v>17792</v>
       </c>
       <c r="J72" s="8">
         <v>5000</v>
@@ -70920,10 +71553,10 @@
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A73" s="4">
-        <v>44362</v>
+        <v>44327</v>
       </c>
       <c r="B73" s="4">
-        <v>44365</v>
+        <v>44330</v>
       </c>
       <c r="C73" s="9" t="s">
         <v>161</v>
@@ -70935,37 +71568,39 @@
         <v>295</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="G73" s="5"/>
+        <v>30</v>
+      </c>
+      <c r="G73" s="5" t="s">
+        <v>160</v>
+      </c>
       <c r="H73" s="8">
-        <v>21050</v>
+        <v>2903</v>
       </c>
       <c r="I73" s="8">
-        <v>18410</v>
+        <v>17225</v>
       </c>
       <c r="J73" s="8">
-        <v>38753</v>
+        <v>5000</v>
       </c>
       <c r="K73" s="19">
-        <v>3753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A74" s="4">
-        <v>45243</v>
+        <v>44350</v>
       </c>
       <c r="B74" s="4">
-        <v>45247</v>
+        <v>44355</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>230</v>
+        <v>161</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F74" s="5" t="s">
         <v>30</v>
@@ -70973,56 +71608,124 @@
       <c r="G74" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="H74" s="19">
-        <v>180143</v>
-      </c>
-      <c r="I74" s="19">
-        <v>12456</v>
+      <c r="H74" s="8">
+        <v>2819</v>
+      </c>
+      <c r="I74" s="8">
+        <v>17736</v>
       </c>
       <c r="J74" s="8">
-        <v>224386</v>
-      </c>
-      <c r="K74" s="21">
+        <v>5000</v>
+      </c>
+      <c r="K74" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A75" s="4">
-        <v>45664</v>
+        <v>44362</v>
       </c>
       <c r="B75" s="4">
-        <v>45671</v>
+        <v>44365</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>230</v>
+        <v>161</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>159</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>67</v>
+        <v>295</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>298</v>
       </c>
       <c r="G75" s="5"/>
-      <c r="H75" s="21">
+      <c r="H75" s="8">
+        <v>21050</v>
+      </c>
+      <c r="I75" s="8">
+        <v>18410</v>
+      </c>
+      <c r="J75" s="8">
+        <v>38753</v>
+      </c>
+      <c r="K75" s="19">
+        <v>3753</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A76" s="4">
+        <v>45243</v>
+      </c>
+      <c r="B76" s="4">
+        <v>45247</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G76" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H76" s="19">
         <v>180143</v>
       </c>
-      <c r="I75" s="21">
+      <c r="I76" s="19">
+        <v>12456</v>
+      </c>
+      <c r="J76" s="8">
+        <v>224386</v>
+      </c>
+      <c r="K76" s="21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A77" s="4">
+        <v>45664</v>
+      </c>
+      <c r="B77" s="4">
+        <v>45671</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="G77" s="5"/>
+      <c r="H77" s="21">
+        <v>180143</v>
+      </c>
+      <c r="I77" s="21">
         <v>15148</v>
       </c>
-      <c r="J75" s="21">
+      <c r="J77" s="21">
         <v>272881</v>
       </c>
-      <c r="K75" s="19">
+      <c r="K77" s="19">
         <v>48494</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K65" xr:uid="{00000000-0009-0000-0000-000007000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K75">
-      <sortCondition ref="C1:C65"/>
+  <autoFilter ref="A1:K67" xr:uid="{00000000-0009-0000-0000-000007000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K77">
+      <sortCondition ref="C1:C67"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="18"/>
